--- a/output/pdf_financials_xlsx/TWM.xlsx
+++ b/output/pdf_financials_xlsx/TWM.xlsx
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.372</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>8.01</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>52.494</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>5.967</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>5.785</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>15.8</v>
@@ -2237,19 +2237,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>3.899</v>
+        <v>4.271</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>8.01</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>52.494</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>5.967</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>5.785</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>15.8</v>
@@ -2681,19 +2681,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.202</v>
+        <v>0.83</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>15.367</v>
+        <v>7.357</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>64.819</v>
+        <v>12.325</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>30.024</v>
+        <v>24.057</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>27.039</v>
+        <v>21.254</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>44.3</v>
@@ -19118,7 +19118,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E205" s="5" t="n">

--- a/output/pdf_financials_xlsx/TWM.xlsx
+++ b/output/pdf_financials_xlsx/TWM.xlsx
@@ -4868,7 +4868,7 @@
         <v>19.8</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0</v>
+        <v>37.3</v>
       </c>
       <c r="J106" s="3" t="n">
         <v>0</v>
@@ -5004,10 +5004,10 @@
         <v>0</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>5.835</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>12.685</v>
       </c>
       <c r="G110" s="3" t="n">
         <v>0</v>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>0</v>
+        <v>-7.023</v>
       </c>
       <c r="C114" s="3" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>2.299</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>6.38</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>0</v>
@@ -31874,7 +31874,11 @@
           <t>Deferred income tax recovery 15</t>
         </is>
       </c>
-      <c r="D402" t="inlineStr"/>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E402" t="inlineStr">
         <is>
           <t>-</t>
@@ -33922,7 +33926,11 @@
           <t>Deferred income tax recovery 16</t>
         </is>
       </c>
-      <c r="D434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E434" t="inlineStr">
         <is>
           <t>-</t>
@@ -35616,7 +35624,11 @@
           <t>Changes in non‐cash operating working capital 22</t>
         </is>
       </c>
-      <c r="D460" t="inlineStr"/>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E460" t="inlineStr">
         <is>
           <t>-</t>
@@ -37062,7 +37074,11 @@
           <t>Deferred income tax expense 15</t>
         </is>
       </c>
-      <c r="D482" t="inlineStr"/>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E482" t="inlineStr">
         <is>
           <t>-</t>
@@ -38484,7 +38500,11 @@
           <t>Accretion 17</t>
         </is>
       </c>
-      <c r="D504" t="inlineStr"/>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E504" t="inlineStr">
         <is>
           <t>-</t>
@@ -38740,7 +38760,11 @@
           <t>Deferred income tax expense (recovery) 14</t>
         </is>
       </c>
-      <c r="D508" t="inlineStr"/>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E508" t="inlineStr">
         <is>
           <t>-</t>
@@ -40816,7 +40840,11 @@
           <t>Deferred income tax expense 10</t>
         </is>
       </c>
-      <c r="D540" t="inlineStr"/>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E540" t="inlineStr">
         <is>
           <t>-</t>
@@ -41988,7 +42016,11 @@
           <t>Deferred income tax expense 9</t>
         </is>
       </c>
-      <c r="D558" t="inlineStr"/>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E558" t="inlineStr">
         <is>
           <t>-</t>
@@ -42518,7 +42550,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D566" t="inlineStr"/>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E566" s="5" t="n">
         <v>2.299</v>
       </c>
@@ -43178,7 +43214,11 @@
           <t>Deferred income tax expense 8</t>
         </is>
       </c>
-      <c r="D576" t="inlineStr"/>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E576" t="inlineStr">
         <is>
           <t>-</t>
@@ -43516,7 +43556,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D581" t="inlineStr"/>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E581" s="5" t="n">
         <v>-7.023</v>
       </c>
